--- a/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_ฉะเชิงเทรา_ปีงบ69.xlsx
+++ b/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_ฉะเชิงเทรา_ปีงบ69.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Report" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$M$106</definedName>
+    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$N$106</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
   <si>
     <t xml:space="preserve">รายงานการตรวจวัดค่าแรงดันน้ำ</t>
   </si>
@@ -322,6 +322,48 @@
         <family val="2"/>
         <charset val="222"/>
       </rPr>
+      <t xml:space="preserve">เม</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">. 69</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
       <t xml:space="preserve">ก</t>
     </r>
     <r>
@@ -2246,7 +2288,7 @@
     <t xml:space="preserve">พิมพ์รายงานวันที่</t>
   </si>
   <si>
-    <t xml:space="preserve">4/3/2569</t>
+    <t xml:space="preserve">3/4/2569</t>
   </si>
   <si>
     <t xml:space="preserve">หน้าที่</t>
@@ -2459,7 +2501,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:W111"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.6"/>
@@ -2473,15 +2515,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="1.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="1.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="5.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="0.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="0.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,11 +2546,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -2528,11 +2572,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -2553,11 +2598,12 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -2573,6 +2619,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -2607,6 +2654,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2623,18 +2673,19 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>2.6</v>
@@ -2653,9 +2704,12 @@
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2664,12 +2718,12 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.9</v>
@@ -2688,9 +2742,12 @@
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2699,7 +2756,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -2723,9 +2780,12 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2734,12 +2794,12 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="7" t="n">
-        <v>2.3</v>
+        <v>2.316666</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>2.4</v>
@@ -2758,9 +2818,12 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2769,12 +2832,12 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="7" t="n">
-        <v>0.54</v>
+        <v>0.533333</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.5</v>
@@ -2793,9 +2856,12 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2804,12 +2870,12 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="7" t="n">
-        <v>2.18</v>
+        <v>2.183333</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>2.2</v>
@@ -2828,9 +2894,12 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2839,12 +2908,12 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="7" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.5</v>
@@ -2863,9 +2932,12 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2874,12 +2946,12 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="7" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.7</v>
@@ -2898,9 +2970,12 @@
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2909,12 +2984,12 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="7" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.7</v>
@@ -2933,9 +3008,12 @@
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2944,12 +3022,12 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="7" t="n">
-        <v>0.72</v>
+        <v>0.733333</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.8</v>
@@ -2968,9 +3046,12 @@
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2979,7 +3060,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -3003,9 +3084,12 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3014,7 +3098,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -3038,9 +3122,12 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3049,12 +3136,12 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="n">
-        <v>1.34</v>
+        <v>1.333333</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.3</v>
@@ -3073,9 +3160,12 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3084,12 +3174,12 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="7" t="n">
-        <v>2.28</v>
+        <v>2.283333</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.3</v>
@@ -3108,9 +3198,12 @@
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3119,12 +3212,12 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="7" t="n">
-        <v>1.54</v>
+        <v>1.533333</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.5</v>
@@ -3143,9 +3236,12 @@
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3154,12 +3250,12 @@
         <v>16</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="7" t="n">
-        <v>1.2</v>
+        <v>1.183333</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1.1</v>
@@ -3178,9 +3274,12 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3189,12 +3288,12 @@
         <v>17</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.2</v>
@@ -3213,9 +3312,12 @@
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3224,12 +3326,12 @@
         <v>18</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="7" t="n">
-        <v>1.3</v>
+        <v>1.283333</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.2</v>
@@ -3248,9 +3350,12 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3259,12 +3364,12 @@
         <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="n">
-        <v>2.26</v>
+        <v>2.283333</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.4</v>
@@ -3283,9 +3388,12 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3294,12 +3402,12 @@
         <v>20</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="n">
-        <v>2.28</v>
+        <v>2.266666</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>2.2</v>
@@ -3318,9 +3426,12 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3329,12 +3440,12 @@
         <v>21</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="n">
-        <v>1.18</v>
+        <v>1.183333</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.1</v>
@@ -3353,9 +3464,12 @@
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3364,12 +3478,12 @@
         <v>22</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="7" t="n">
-        <v>2.28</v>
+        <v>2.283333</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>2.2</v>
@@ -3388,9 +3502,12 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3399,12 +3516,12 @@
         <v>23</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="7" t="n">
-        <v>2.42</v>
+        <v>2.416666</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>2.5</v>
@@ -3423,9 +3540,12 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3434,12 +3554,12 @@
         <v>24</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="7" t="n">
-        <v>2.08</v>
+        <v>2.066666</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>2</v>
@@ -3458,9 +3578,12 @@
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3469,12 +3592,12 @@
         <v>25</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="7" t="n">
-        <v>2.32</v>
+        <v>2.316666</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2.2</v>
@@ -3493,9 +3616,12 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3504,12 +3630,12 @@
         <v>26</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>0.7</v>
@@ -3528,9 +3654,12 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3539,12 +3668,12 @@
         <v>27</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="7" t="n">
-        <v>0.82</v>
+        <v>0.833333</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.7</v>
@@ -3563,9 +3692,12 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3574,12 +3706,12 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="7" t="n">
-        <v>2.24</v>
+        <v>2.233333</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>2.3</v>
@@ -3598,9 +3730,12 @@
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3609,7 +3744,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -3633,9 +3768,12 @@
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3644,12 +3782,12 @@
         <v>30</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="7" t="n">
-        <v>0.72</v>
+        <v>0.716666</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.7</v>
@@ -3668,9 +3806,12 @@
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3679,12 +3820,12 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="7" t="n">
-        <v>1.12</v>
+        <v>1.133333</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1</v>
@@ -3703,9 +3844,12 @@
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3714,12 +3858,12 @@
         <v>32</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="7" t="n">
-        <v>1.78</v>
+        <v>1.766666</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.9</v>
@@ -3738,9 +3882,12 @@
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3749,12 +3896,12 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="7" t="n">
-        <v>1.34</v>
+        <v>1.366666</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.4</v>
@@ -3773,9 +3920,12 @@
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3784,12 +3934,12 @@
         <v>34</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>1.3</v>
@@ -3808,9 +3958,12 @@
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3819,12 +3972,12 @@
         <v>35</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="7" t="n">
-        <v>0.74</v>
+        <v>0.733333</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.8</v>
@@ -3843,9 +3996,12 @@
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3854,12 +4010,12 @@
         <v>36</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="7" t="n">
-        <v>0.9</v>
+        <v>0.883333</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>1</v>
@@ -3878,9 +4034,12 @@
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3889,12 +4048,12 @@
         <v>37</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="7" t="n">
-        <v>0.82</v>
+        <v>0.816666</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>0.9</v>
@@ -3913,9 +4072,12 @@
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3924,12 +4086,12 @@
         <v>38</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="7" t="n">
-        <v>0.92</v>
+        <v>0.916666</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>1</v>
@@ -3948,9 +4110,12 @@
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3959,12 +4124,12 @@
         <v>39</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="7" t="n">
-        <v>2.24</v>
+        <v>2.266666</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>2.2</v>
@@ -3983,9 +4148,12 @@
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3994,12 +4162,12 @@
         <v>40</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="7" t="n">
-        <v>1.08</v>
+        <v>1.066666</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>1.2</v>
@@ -4018,9 +4186,12 @@
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4029,12 +4200,12 @@
         <v>41</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="7" t="n">
-        <v>1.2</v>
+        <v>1.216666</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>1.3</v>
@@ -4053,9 +4224,12 @@
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4064,12 +4238,12 @@
         <v>42</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="7" t="n">
-        <v>1.16</v>
+        <v>1.183333</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>1.3</v>
@@ -4088,9 +4262,12 @@
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4099,7 +4276,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -4123,9 +4300,12 @@
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4134,12 +4314,12 @@
         <v>44</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="7" t="n">
-        <v>2.3</v>
+        <v>2.316666</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>2.4</v>
@@ -4158,9 +4338,12 @@
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4169,7 +4352,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -4193,9 +4376,12 @@
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4204,12 +4390,12 @@
         <v>46</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="7" t="n">
-        <v>2.28</v>
+        <v>2.266666</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>2.2</v>
@@ -4228,9 +4414,12 @@
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4239,12 +4428,12 @@
         <v>47</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="7" t="n">
-        <v>1.82</v>
+        <v>1.816666</v>
       </c>
       <c r="F53" s="9" t="n">
         <v>1.8</v>
@@ -4263,9 +4452,12 @@
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4274,12 +4466,12 @@
         <v>48</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="F54" s="9" t="n">
         <v>1.8</v>
@@ -4298,9 +4490,12 @@
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4309,12 +4504,12 @@
         <v>49</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="7" t="n">
-        <v>1.82</v>
+        <v>1.816666</v>
       </c>
       <c r="F55" s="9" t="n">
         <v>1.8</v>
@@ -4333,9 +4528,12 @@
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4344,12 +4542,12 @@
         <v>50</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="F56" s="9" t="n">
         <v>2.3</v>
@@ -4368,9 +4566,12 @@
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4379,12 +4580,12 @@
         <v>51</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="7" t="n">
-        <v>2.34</v>
+        <v>2.333333</v>
       </c>
       <c r="F57" s="9" t="n">
         <v>2.3</v>
@@ -4403,9 +4604,12 @@
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4414,12 +4618,12 @@
         <v>52</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="7" t="n">
-        <v>2.46</v>
+        <v>2.483333</v>
       </c>
       <c r="F58" s="9" t="n">
         <v>2.6</v>
@@ -4438,9 +4642,12 @@
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4449,12 +4656,12 @@
         <v>53</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="F59" s="9" t="n">
         <v>2.6</v>
@@ -4473,9 +4680,12 @@
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4484,12 +4694,12 @@
         <v>54</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="F60" s="9" t="n">
         <v>2.4</v>
@@ -4508,9 +4718,12 @@
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4519,12 +4732,12 @@
         <v>55</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="7" t="n">
-        <v>1.52</v>
+        <v>1.516666</v>
       </c>
       <c r="F61" s="9" t="n">
         <v>1.5</v>
@@ -4543,9 +4756,12 @@
       </c>
       <c r="K61" s="9"/>
       <c r="L61" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4554,12 +4770,12 @@
         <v>56</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="E62" s="7" t="n">
-        <v>2</v>
+        <v>1.983333</v>
       </c>
       <c r="F62" s="9" t="n">
         <v>1.9</v>
@@ -4578,9 +4794,12 @@
       </c>
       <c r="K62" s="9"/>
       <c r="L62" s="9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4589,12 +4808,12 @@
         <v>57</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="7" t="n">
-        <v>1.24</v>
+        <v>1.233333</v>
       </c>
       <c r="F63" s="9" t="n">
         <v>1.2</v>
@@ -4613,9 +4832,12 @@
       </c>
       <c r="K63" s="9"/>
       <c r="L63" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4624,12 +4846,12 @@
         <v>58</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="F64" s="9" t="n">
         <v>1.4</v>
@@ -4648,9 +4870,12 @@
       </c>
       <c r="K64" s="9"/>
       <c r="L64" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4659,12 +4884,12 @@
         <v>59</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="7" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="F65" s="9" t="n">
         <v>0.7</v>
@@ -4683,9 +4908,12 @@
       </c>
       <c r="K65" s="9"/>
       <c r="L65" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4694,12 +4922,12 @@
         <v>60</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="7" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="F66" s="9" t="n">
         <v>0.7</v>
@@ -4718,9 +4946,12 @@
       </c>
       <c r="K66" s="9"/>
       <c r="L66" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4729,12 +4960,12 @@
         <v>61</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="7" t="n">
-        <v>0.66</v>
+        <v>0.666666</v>
       </c>
       <c r="F67" s="9" t="n">
         <v>0.6</v>
@@ -4753,9 +4984,12 @@
       </c>
       <c r="K67" s="9"/>
       <c r="L67" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4764,12 +4998,12 @@
         <v>62</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="7" t="n">
-        <v>0.78</v>
+        <v>0.766666</v>
       </c>
       <c r="F68" s="9" t="n">
         <v>0.8</v>
@@ -4788,9 +5022,12 @@
       </c>
       <c r="K68" s="9"/>
       <c r="L68" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4799,12 +5036,12 @@
         <v>63</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="7" t="n">
-        <v>0.88</v>
+        <v>0.866666</v>
       </c>
       <c r="F69" s="9" t="n">
         <v>0.9</v>
@@ -4823,9 +5060,12 @@
       </c>
       <c r="K69" s="9"/>
       <c r="L69" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4834,7 +5074,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -4858,9 +5098,12 @@
       </c>
       <c r="K70" s="9"/>
       <c r="L70" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4869,12 +5112,12 @@
         <v>65</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="7" t="n">
-        <v>0.8</v>
+        <v>0.783333</v>
       </c>
       <c r="F71" s="9" t="n">
         <v>0.8</v>
@@ -4893,9 +5136,12 @@
       </c>
       <c r="K71" s="9"/>
       <c r="L71" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4904,7 +5150,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
@@ -4928,9 +5174,12 @@
       </c>
       <c r="K72" s="9"/>
       <c r="L72" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4939,12 +5188,12 @@
         <v>67</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="7" t="n">
-        <v>2.2</v>
+        <v>2.233333</v>
       </c>
       <c r="F73" s="9" t="n">
         <v>2.2</v>
@@ -4963,9 +5212,12 @@
       </c>
       <c r="K73" s="9"/>
       <c r="L73" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4974,12 +5226,12 @@
         <v>68</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="7" t="n">
-        <v>2.3</v>
+        <v>2.316666</v>
       </c>
       <c r="F74" s="9" t="n">
         <v>2.3</v>
@@ -4998,9 +5250,12 @@
       </c>
       <c r="K74" s="9"/>
       <c r="L74" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5009,12 +5264,12 @@
         <v>69</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="F75" s="9" t="n">
         <v>2.3</v>
@@ -5033,9 +5288,12 @@
       </c>
       <c r="K75" s="9"/>
       <c r="L75" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5044,12 +5302,12 @@
         <v>70</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="7" t="n">
-        <v>2.26</v>
+        <v>2.266666</v>
       </c>
       <c r="F76" s="9" t="n">
         <v>2.2</v>
@@ -5068,9 +5326,12 @@
       </c>
       <c r="K76" s="9"/>
       <c r="L76" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5079,12 +5340,12 @@
         <v>71</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="F77" s="9" t="n">
         <v>2.2</v>
@@ -5103,9 +5364,12 @@
       </c>
       <c r="K77" s="9"/>
       <c r="L77" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5114,12 +5378,12 @@
         <v>72</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
       <c r="E78" s="7" t="n">
-        <v>2.22</v>
+        <v>2.233333</v>
       </c>
       <c r="F78" s="9" t="n">
         <v>2.2</v>
@@ -5138,9 +5402,12 @@
       </c>
       <c r="K78" s="9"/>
       <c r="L78" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5149,12 +5416,12 @@
         <v>73</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="7" t="n">
-        <v>1.1</v>
+        <v>1.083333</v>
       </c>
       <c r="F79" s="9" t="n">
         <v>1.1</v>
@@ -5173,9 +5440,12 @@
       </c>
       <c r="K79" s="9"/>
       <c r="L79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5184,12 +5454,12 @@
         <v>74</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
       <c r="E80" s="7" t="n">
-        <v>1.04</v>
+        <v>1.016666</v>
       </c>
       <c r="F80" s="9" t="n">
         <v>1.1</v>
@@ -5208,9 +5478,12 @@
       </c>
       <c r="K80" s="9"/>
       <c r="L80" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5219,12 +5492,12 @@
         <v>75</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="F81" s="9" t="n">
         <v>2.2</v>
@@ -5243,9 +5516,12 @@
       </c>
       <c r="K81" s="9"/>
       <c r="L81" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5254,12 +5530,12 @@
         <v>76</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="F82" s="9" t="n">
         <v>2.4</v>
@@ -5278,9 +5554,12 @@
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5289,7 +5568,7 @@
         <v>77</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
@@ -5313,9 +5592,12 @@
       </c>
       <c r="K83" s="9"/>
       <c r="L83" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5324,12 +5606,12 @@
         <v>78</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
       <c r="E84" s="7" t="n">
-        <v>2.38</v>
+        <v>2.383333</v>
       </c>
       <c r="F84" s="9" t="n">
         <v>2.3</v>
@@ -5348,9 +5630,12 @@
       </c>
       <c r="K84" s="9"/>
       <c r="L84" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5359,7 +5644,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
@@ -5383,9 +5668,12 @@
       </c>
       <c r="K85" s="9"/>
       <c r="L85" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5394,12 +5682,12 @@
         <v>80</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="7" t="n">
-        <v>2.26</v>
+        <v>2.266666</v>
       </c>
       <c r="F86" s="9" t="n">
         <v>2.2</v>
@@ -5418,9 +5706,12 @@
       </c>
       <c r="K86" s="9"/>
       <c r="L86" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5429,12 +5720,12 @@
         <v>81</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
       <c r="E87" s="7" t="n">
-        <v>2.06</v>
+        <v>2.083333</v>
       </c>
       <c r="F87" s="9" t="n">
         <v>2.1</v>
@@ -5453,9 +5744,12 @@
       </c>
       <c r="K87" s="9"/>
       <c r="L87" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5464,12 +5758,12 @@
         <v>82</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
       <c r="E88" s="7" t="n">
-        <v>2.22</v>
+        <v>2.233333</v>
       </c>
       <c r="F88" s="9" t="n">
         <v>2.2</v>
@@ -5488,9 +5782,12 @@
       </c>
       <c r="K88" s="9"/>
       <c r="L88" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5499,12 +5796,12 @@
         <v>83</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
       <c r="E89" s="7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="F89" s="9" t="n">
         <v>2.2</v>
@@ -5523,9 +5820,12 @@
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5534,12 +5834,12 @@
         <v>84</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
       <c r="E90" s="7" t="n">
-        <v>1.84</v>
+        <v>1.833333</v>
       </c>
       <c r="F90" s="9" t="n">
         <v>1.9</v>
@@ -5558,9 +5858,12 @@
       </c>
       <c r="K90" s="9"/>
       <c r="L90" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5569,12 +5872,12 @@
         <v>85</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="7" t="n">
-        <v>0.8</v>
+        <v>0.783333</v>
       </c>
       <c r="F91" s="9" t="n">
         <v>0.8</v>
@@ -5593,9 +5896,12 @@
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5604,12 +5910,12 @@
         <v>86</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
       <c r="E92" s="7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="F92" s="9" t="n">
         <v>2.2</v>
@@ -5628,9 +5934,12 @@
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5639,12 +5948,12 @@
         <v>87</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
       <c r="E93" s="7" t="n">
-        <v>0.8</v>
+        <v>0.816666</v>
       </c>
       <c r="F93" s="9" t="n">
         <v>0.8</v>
@@ -5663,9 +5972,12 @@
       </c>
       <c r="K93" s="9"/>
       <c r="L93" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5674,12 +5986,12 @@
         <v>88</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94" s="8"/>
       <c r="D94" s="8"/>
       <c r="E94" s="7" t="n">
-        <v>0.8</v>
+        <v>0.816666</v>
       </c>
       <c r="F94" s="9" t="n">
         <v>0.8</v>
@@ -5698,9 +6010,12 @@
       </c>
       <c r="K94" s="9"/>
       <c r="L94" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5709,12 +6024,12 @@
         <v>89</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
       <c r="E95" s="7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="F95" s="9" t="n">
         <v>2.2</v>
@@ -5733,9 +6048,12 @@
       </c>
       <c r="K95" s="9"/>
       <c r="L95" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5744,12 +6062,12 @@
         <v>90</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
       <c r="E96" s="7" t="n">
-        <v>2.16</v>
+        <v>2.166666</v>
       </c>
       <c r="F96" s="9" t="n">
         <v>2.1</v>
@@ -5768,9 +6086,12 @@
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5779,12 +6100,12 @@
         <v>91</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="7" t="n">
-        <v>2.32</v>
+        <v>2.316666</v>
       </c>
       <c r="F97" s="9" t="n">
         <v>2.4</v>
@@ -5803,9 +6124,12 @@
       </c>
       <c r="K97" s="9"/>
       <c r="L97" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5814,12 +6138,12 @@
         <v>92</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="F98" s="9" t="n">
         <v>2.4</v>
@@ -5838,9 +6162,12 @@
       </c>
       <c r="K98" s="9"/>
       <c r="L98" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5849,12 +6176,12 @@
         <v>93</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
       <c r="E99" s="7" t="n">
-        <v>2.18</v>
+        <v>2.216666</v>
       </c>
       <c r="F99" s="9" t="n">
         <v>2.2</v>
@@ -5873,9 +6200,12 @@
       </c>
       <c r="K99" s="9"/>
       <c r="L99" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5884,12 +6214,12 @@
         <v>94</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c r="E100" s="7" t="n">
-        <v>1.06</v>
+        <v>1.066666</v>
       </c>
       <c r="F100" s="9" t="n">
         <v>1.1</v>
@@ -5908,9 +6238,12 @@
       </c>
       <c r="K100" s="9"/>
       <c r="L100" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5919,12 +6252,12 @@
         <v>95</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="7" t="n">
-        <v>2.3</v>
+        <v>2.333333</v>
       </c>
       <c r="F101" s="9" t="n">
         <v>2.2</v>
@@ -5943,9 +6276,12 @@
       </c>
       <c r="K101" s="9"/>
       <c r="L101" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5954,12 +6290,12 @@
         <v>96</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="F102" s="9" t="n">
         <v>2.4</v>
@@ -5978,9 +6314,12 @@
       </c>
       <c r="K102" s="9"/>
       <c r="L102" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5989,12 +6328,12 @@
         <v>97</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c r="E103" s="7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="F103" s="9" t="n">
         <v>1.9</v>
@@ -6013,9 +6352,12 @@
       </c>
       <c r="K103" s="9"/>
       <c r="L103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6024,12 +6366,12 @@
         <v>98</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
       <c r="E104" s="7" t="n">
-        <v>1.78</v>
+        <v>1.783333</v>
       </c>
       <c r="F104" s="9" t="n">
         <v>1.7</v>
@@ -6048,9 +6390,12 @@
       </c>
       <c r="K104" s="9"/>
       <c r="L104" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6059,12 +6404,12 @@
         <v>99</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="7" t="n">
-        <v>1.44</v>
+        <v>1.466666</v>
       </c>
       <c r="F105" s="9" t="n">
         <v>1.3</v>
@@ -6083,9 +6428,12 @@
       </c>
       <c r="K105" s="9"/>
       <c r="L105" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6094,12 +6442,12 @@
         <v>100</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
       <c r="E106" s="7" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="F106" s="9" t="n">
         <v>0.8</v>
@@ -6118,9 +6466,12 @@
       </c>
       <c r="K106" s="9"/>
       <c r="L106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6147,10 +6498,11 @@
       <c r="T107" s="10"/>
       <c r="U107" s="10"/>
       <c r="V107" s="10"/>
+      <c r="W107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -6162,7 +6514,7 @@
       <c r="I108" s="11"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" s="11"/>
@@ -6175,10 +6527,11 @@
       <c r="T108" s="11"/>
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
+      <c r="W108" s="11"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
@@ -6190,7 +6543,7 @@
       <c r="I109" s="11"/>
       <c r="J109" s="11"/>
       <c r="K109" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L109" s="11"/>
       <c r="M109" s="11"/>
@@ -6203,10 +6556,11 @@
       <c r="T109" s="11"/>
       <c r="U109" s="11"/>
       <c r="V109" s="11"/>
+      <c r="W109" s="11"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -6218,7 +6572,7 @@
       <c r="I110" s="12"/>
       <c r="J110" s="12"/>
       <c r="K110" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110" s="12"/>
@@ -6231,6 +6585,7 @@
       <c r="T110" s="12"/>
       <c r="U110" s="12"/>
       <c r="V110" s="12"/>
+      <c r="W110" s="12"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="13"/>
@@ -6244,39 +6599,40 @@
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
       <c r="K111" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L111" s="13"/>
       <c r="M111" s="13"/>
       <c r="N111" s="13"/>
-      <c r="O111" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="P111" s="13" t="s">
+      <c r="O111" s="13"/>
+      <c r="P111" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="Q111" s="13"/>
-      <c r="R111" s="15" t="s">
+      <c r="Q111" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="S111" s="12" t="s">
+      <c r="R111" s="13"/>
+      <c r="S111" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="T111" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="U111" s="10"/>
+      <c r="T111" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="U111" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="V111" s="10"/>
+      <c r="W111" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="226">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C3:Q3"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B5:D5"/>
@@ -6484,18 +6840,18 @@
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="J106:K106"/>
     <mergeCell ref="A107:J107"/>
-    <mergeCell ref="K107:V107"/>
+    <mergeCell ref="K107:W107"/>
     <mergeCell ref="A108:J108"/>
-    <mergeCell ref="K108:V108"/>
+    <mergeCell ref="K108:W108"/>
     <mergeCell ref="A109:J109"/>
-    <mergeCell ref="K109:V109"/>
+    <mergeCell ref="K109:W109"/>
     <mergeCell ref="A110:J110"/>
-    <mergeCell ref="K110:V110"/>
+    <mergeCell ref="K110:W110"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="D111:J111"/>
-    <mergeCell ref="K111:N111"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="K111:O111"/>
+    <mergeCell ref="Q111:R111"/>
+    <mergeCell ref="V111:W111"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
